--- a/results_table.xlsx
+++ b/results_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>config</t>
   </si>
@@ -31,55 +31,52 @@
     <t>all_optimal</t>
   </si>
   <si>
-    <t>{"solver": "simplex", "presolve": "on", "simplex_strategy": 1, "parallel": "off", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "on", "simplex_strategy": 1, "parallel": "off", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "off", "simplex_strategy": 1, "parallel": "off", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "off", "simplex_strategy": 0, "parallel": "off", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "off", "simplex_strategy": 2, "parallel": "off", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "off", "simplex_strategy": 3, "parallel": "off", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "off", "simplex_strategy": 0, "parallel": "on", "scaling": "on"}</t>
-  </si>
-  <si>
-    <t>{"solver": "ipm", "presolve": "off", "simplex_strategy": 0, "parallel": "off", "scaling": "off"}</t>
+    <t>{"solver": "simplex", "simplex_strategy": 1, "presolve": "on", "parallel": "off", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "ipm", "simplex_strategy": 1, "presolve": "on", "parallel": "off", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "simplex", "simplex_strategy": 0, "presolve": "on", "parallel": "off", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "simplex", "simplex_strategy": 2, "presolve": "on", "parallel": "off", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "simplex", "simplex_strategy": 3, "presolve": "on", "parallel": "off", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "ipm", "simplex_strategy": 1, "presolve": "off", "parallel": "off", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "ipm", "simplex_strategy": 1, "presolve": "off", "parallel": "on", "scaling": "on"}</t>
+  </si>
+  <si>
+    <t>{"solver": "ipm", "simplex_strategy": 1, "presolve": "off", "parallel": "off", "scaling": "off"}</t>
   </si>
   <si>
     <t>baseline</t>
   </si>
   <si>
-    <t>test solver=simplex</t>
-  </si>
-  <si>
-    <t>test solver=ipm</t>
+    <t>solver=ipm strategy=1</t>
+  </si>
+  <si>
+    <t>solver=simplex strategy=0</t>
+  </si>
+  <si>
+    <t>solver=simplex strategy=1</t>
+  </si>
+  <si>
+    <t>solver=simplex strategy=2</t>
+  </si>
+  <si>
+    <t>solver=simplex strategy=3</t>
   </si>
   <si>
     <t>test presolve=on</t>
   </si>
   <si>
     <t>test presolve=off</t>
-  </si>
-  <si>
-    <t>test simplex_strategy=0</t>
-  </si>
-  <si>
-    <t>test simplex_strategy=1</t>
-  </si>
-  <si>
-    <t>test simplex_strategy=2</t>
-  </si>
-  <si>
-    <t>test simplex_strategy=3</t>
   </si>
   <si>
     <t>test parallel=on</t>
@@ -452,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -480,10 +477,10 @@
         <v>13</v>
       </c>
       <c r="C2">
-        <v>65.64406845904887</v>
+        <v>64.40700000000288</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -491,16 +488,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3">
-        <v>66.21338504203595</v>
+        <v>2.281000000002678</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -508,16 +505,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4">
-        <v>1.645338332979009</v>
+        <v>64.14099999999962</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -525,16 +522,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5">
-        <v>1.622031165985391</v>
+        <v>64.34400000000096</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -542,16 +539,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6">
-        <v>1.592288250103593</v>
+        <v>60.75</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -559,16 +556,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7">
-        <v>1.58430004119873</v>
+        <v>69.61000000000058</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -576,16 +573,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8">
-        <v>1.587496457854286</v>
+        <v>2.09400000000096</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -593,16 +590,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9">
-        <v>1.59839095803909</v>
+        <v>2.03099999999904</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -610,16 +607,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10">
-        <v>1.597729041939601</v>
+        <v>2.139999999999418</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -627,16 +624,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11">
-        <v>1.552658833796158</v>
+        <v>2.218000000000757</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -644,16 +641,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12">
-        <v>1.550482999999076</v>
+        <v>2.188000000001921</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -661,35 +658,18 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
       <c r="C13">
-        <v>1.567128916969523</v>
+        <v>2.140999999999622</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14">
-        <v>1.565690958173946</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="b">
         <v>0</v>
       </c>
     </row>
